--- a/sheets/조재수대금교본/검수/여자의 일생.xlsx
+++ b/sheets/조재수대금교본/검수/여자의 일생.xlsx
@@ -2679,8 +2679,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㒣
-‹</t>
+㒣</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -2700,8 +2699,7 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-應潢
-‹</t>
+應潢</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -2762,8 +2760,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -2805,30 +2802,18 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㒣
-黃⊏</t>
+黃</t>
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -2940,37 +2925,23 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
@@ -3006,7 +2977,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3018,8 +2989,7 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -3039,7 +3009,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
+          <t xml:space="preserve">仲
 姑仲</t>
         </is>
       </c>
@@ -3065,8 +3035,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -3112,8 +3081,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="I14" s="24"/>

--- a/sheets/조재수대금교본/검수/여자의 일생.xlsx
+++ b/sheets/조재수대금교본/검수/여자의 일생.xlsx
@@ -2809,7 +2809,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㒣
-黃</t>
+黃⊏</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2977,7 +2977,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3009,7 +3009,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ʒ
 姑仲</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/여자의 일생.xlsx
+++ b/sheets/조재수대금교본/검수/여자의 일생.xlsx
@@ -2638,24 +2638,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2888,7 +2888,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2916,7 +2916,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3101,6 +3101,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>